--- a/runs/RELX/2026-10-14/bear/scratch/gs_strict_5yw_g5/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/gs_strict_5yw_g5/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2195.890601211349</v>
+        <v>2238.418063205629</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.087505</v>
+        <v>0.0822242</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.08237433914</v>
+        <v>0.077770432084</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11650.44259302692</v>
+        <v>11772.65346842173</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>51707.32763208793</v>
+        <v>56077.69374493908</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>36212.07400146699</v>
+        <v>40033.35177173526</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>47862.51659449391</v>
+        <v>51806.00524015698</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>40865.51659449391</v>
+        <v>44809.00524015698</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>40368.64206441462</v>
+        <v>44397.87221178922</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>23.15041297916127</v>
+        <v>25.46107633392482</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2315.041297916127</v>
+        <v>2546.107633392482</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.1645466265</v>
+        <v>-0.08115928059999999</v>
       </c>
     </row>
   </sheetData>
